--- a/m101/M101 - Fichas de trabajo.xlsx
+++ b/m101/M101 - Fichas de trabajo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dragonnomada/Desktop/GitHub/diplomado-ia-asa/m101/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CBF4D38-45C5-E044-82CD-308601F62991}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BA8971C-AA6E-C448-8600-4CE27C999A65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -895,7 +895,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="48">
+  <borders count="49">
     <border>
       <left/>
       <right/>
@@ -1472,11 +1472,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF063A56"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="85">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1722,6 +1731,12 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2034,13 +2049,13 @@
       <c r="B6" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="C6" s="84" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9"/>
+      <c r="D6" s="84"/>
+      <c r="E6" s="84"/>
+      <c r="F6" s="84"/>
+      <c r="G6" s="84"/>
       <c r="H6" s="2"/>
     </row>
     <row r="7" spans="1:8" ht="28" customHeight="1">
@@ -2048,13 +2063,13 @@
       <c r="B7" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="83" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
+      <c r="D7" s="83"/>
+      <c r="E7" s="83"/>
+      <c r="F7" s="83"/>
+      <c r="G7" s="83"/>
       <c r="H7" s="2"/>
     </row>
     <row r="8" spans="1:8" ht="28" customHeight="1">
@@ -2062,13 +2077,13 @@
       <c r="B8" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="C8" s="83" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
+      <c r="D8" s="83"/>
+      <c r="E8" s="83"/>
+      <c r="F8" s="83"/>
+      <c r="G8" s="83"/>
       <c r="H8" s="2"/>
     </row>
     <row r="9" spans="1:8" ht="28" customHeight="1">
@@ -2076,13 +2091,13 @@
       <c r="B9" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="C9" s="83" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
+      <c r="D9" s="83"/>
+      <c r="E9" s="83"/>
+      <c r="F9" s="83"/>
+      <c r="G9" s="83"/>
       <c r="H9" s="2"/>
     </row>
     <row r="10" spans="1:8">
@@ -2508,9 +2523,13 @@
       <c r="H40" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="6">
     <mergeCell ref="B22:G22"/>
     <mergeCell ref="B3:G3"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="C9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
